--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="referencias_mercado" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="referencias_mercado" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -88,11 +88,79 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -107,13 +175,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -410,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -795,7 +863,7 @@
         </is>
       </c>
       <c r="D11" s="5" t="n">
-        <v>950.992383</v>
+        <v>952.062045</v>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
@@ -829,12 +897,12 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T04:02:01.403Z</t>
+          <t>2026-07-28T21:01:02.150Z</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T10:04:49Z</t>
+          <t>2026-07-28T21:37:15Z</t>
         </is>
       </c>
       <c r="M11" s="4" t="n"/>
@@ -861,7 +929,7 @@
         </is>
       </c>
       <c r="D12" s="5" t="n">
-        <v>836.179073</v>
+        <v>836.511227</v>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
@@ -895,18 +963,146 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T04:02:01.389Z</t>
+          <t>2026-07-28T21:01:02.140Z</t>
         </is>
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T10:04:49Z</t>
+          <t>2026-07-28T21:37:15Z</t>
         </is>
       </c>
       <c r="M12" s="4" t="n"/>
       <c r="N12" s="4" t="inlineStr">
         <is>
           <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_compra</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - compra</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>848.146</v>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="n"/>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-28T21:37:15Z</t>
+        </is>
+      </c>
+      <c r="M13" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N13" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para compra. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_venta</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - venta</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>849.2297</v>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="n"/>
+      <c r="L14" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-28T21:37:15Z</t>
+        </is>
+      </c>
+      <c r="M14" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N14" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para venta. No es tasa oficial.</t>
         </is>
       </c>
     </row>

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1106,6 +1106,266 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>ve_eur_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>EUR paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>963.125001</v>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>VES por EUR</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29T21:01:28.400Z</t>
+        </is>
+      </c>
+      <c r="L15" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29T21:26:05Z</t>
+        </is>
+      </c>
+      <c r="M15" s="4" t="n"/>
+      <c r="N15" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>ve_usd_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>USD paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>839.962502</v>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>VES por USD</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29T21:01:28.328Z</t>
+        </is>
+      </c>
+      <c r="L16" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29T21:26:05Z</t>
+        </is>
+      </c>
+      <c r="M16" s="4" t="n"/>
+      <c r="N16" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_compra</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - compra</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>851.2169</v>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="n"/>
+      <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29T21:26:05Z</t>
+        </is>
+      </c>
+      <c r="M17" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N17" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para compra. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_venta</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - venta</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>848.9599000000001</v>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K18" s="4" t="n"/>
+      <c r="L18" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29T21:26:05Z</t>
+        </is>
+      </c>
+      <c r="M18" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N18" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para venta. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N18"/>
+  <dimension ref="A1:N22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1366,6 +1366,266 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>ve_eur_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>EUR paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>965.332574</v>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>VES por EUR</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-30T21:00:57.226Z</t>
+        </is>
+      </c>
+      <c r="L19" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-30T21:40:43Z</t>
+        </is>
+      </c>
+      <c r="M19" s="4" t="n"/>
+      <c r="N19" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>ve_usd_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>USD paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>837.495512</v>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>VES por USD</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-30T21:00:57.211Z</t>
+        </is>
+      </c>
+      <c r="L20" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-30T21:40:43Z</t>
+        </is>
+      </c>
+      <c r="M20" s="4" t="n"/>
+      <c r="N20" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_compra</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - compra</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>853.8754</v>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K21" s="4" t="n"/>
+      <c r="L21" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-30T21:40:43Z</t>
+        </is>
+      </c>
+      <c r="M21" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N21" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para compra. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_venta</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - venta</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>851.4598999999999</v>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="n"/>
+      <c r="L22" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-30T21:40:43Z</t>
+        </is>
+      </c>
+      <c r="M22" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N22" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para venta. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N22"/>
+  <dimension ref="A1:N26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1626,6 +1626,266 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>ve_eur_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>EUR paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>965.72216</v>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>VES por EUR</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-31T21:01:12.029Z</t>
+        </is>
+      </c>
+      <c r="L23" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-31T21:36:29Z</t>
+        </is>
+      </c>
+      <c r="M23" s="4" t="n"/>
+      <c r="N23" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>ve_usd_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>USD paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>837.701202</v>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>VES por USD</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-31T21:01:12.014Z</t>
+        </is>
+      </c>
+      <c r="L24" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-31T21:36:29Z</t>
+        </is>
+      </c>
+      <c r="M24" s="4" t="n"/>
+      <c r="N24" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_compra</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - compra</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>849.8199</v>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K25" s="4" t="n"/>
+      <c r="L25" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-31T21:36:29Z</t>
+        </is>
+      </c>
+      <c r="M25" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N25" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para compra. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_venta</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - venta</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>844.5888</v>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K26" s="4" t="n"/>
+      <c r="L26" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-31T21:36:29Z</t>
+        </is>
+      </c>
+      <c r="M26" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N26" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para venta. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N26"/>
+  <dimension ref="A1:N30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1886,6 +1886,266 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>ve_eur_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>EUR paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>965.947451</v>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>VES por EUR</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01T21:01:19.158Z</t>
+        </is>
+      </c>
+      <c r="L27" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01T21:23:44Z</t>
+        </is>
+      </c>
+      <c r="M27" s="4" t="n"/>
+      <c r="N27" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>ve_usd_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>USD paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>839.046105</v>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>VES por USD</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01T21:01:19.087Z</t>
+        </is>
+      </c>
+      <c r="L28" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01T21:23:44Z</t>
+        </is>
+      </c>
+      <c r="M28" s="4" t="n"/>
+      <c r="N28" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_compra</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - compra</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>846.1061</v>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K29" s="4" t="n"/>
+      <c r="L29" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01T21:23:44Z</t>
+        </is>
+      </c>
+      <c r="M29" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N29" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para compra. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_venta</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - venta</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>846.3146</v>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K30" s="4" t="n"/>
+      <c r="L30" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01T21:23:44Z</t>
+        </is>
+      </c>
+      <c r="M30" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N30" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para venta. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N30"/>
+  <dimension ref="A1:N34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2146,6 +2146,266 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>ve_eur_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>EUR paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>971.6683420000001</v>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>VES por EUR</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K31" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-02T21:00:58.333Z</t>
+        </is>
+      </c>
+      <c r="L31" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-02T21:23:43Z</t>
+        </is>
+      </c>
+      <c r="M31" s="4" t="n"/>
+      <c r="N31" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>ve_usd_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>USD paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>842.357747</v>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>VES por USD</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-02T21:00:58.323Z</t>
+        </is>
+      </c>
+      <c r="L32" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-02T21:23:43Z</t>
+        </is>
+      </c>
+      <c r="M32" s="4" t="n"/>
+      <c r="N32" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_compra</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - compra</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>845.1733</v>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K33" s="4" t="n"/>
+      <c r="L33" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-02T21:23:43Z</t>
+        </is>
+      </c>
+      <c r="M33" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N33" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para compra. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_venta</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - venta</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>836.1109</v>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K34" s="4" t="n"/>
+      <c r="L34" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-02T21:23:43Z</t>
+        </is>
+      </c>
+      <c r="M34" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N34" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para venta. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N34"/>
+  <dimension ref="A1:N38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2406,6 +2406,266 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>ve_eur_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>EUR paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>969.17255</v>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>VES por EUR</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K35" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-03T21:01:11.014Z</t>
+        </is>
+      </c>
+      <c r="L35" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-03T21:38:39Z</t>
+        </is>
+      </c>
+      <c r="M35" s="4" t="n"/>
+      <c r="N35" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>ve_usd_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>USD paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>842.484253</v>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>VES por USD</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K36" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-03T21:01:10.976Z</t>
+        </is>
+      </c>
+      <c r="L36" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-03T21:38:39Z</t>
+        </is>
+      </c>
+      <c r="M36" s="4" t="n"/>
+      <c r="N36" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_compra</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - compra</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>849.347</v>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K37" s="4" t="n"/>
+      <c r="L37" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-03T21:38:39Z</t>
+        </is>
+      </c>
+      <c r="M37" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N37" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para compra. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_venta</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - venta</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="n">
+        <v>848.9493</v>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I38" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K38" s="4" t="n"/>
+      <c r="L38" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-03T21:38:39Z</t>
+        </is>
+      </c>
+      <c r="M38" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N38" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para venta. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N38"/>
+  <dimension ref="A1:N42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2666,6 +2666,266 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>ve_eur_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>EUR paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="n">
+        <v>967.671711</v>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>VES por EUR</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I39" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K39" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-04T21:01:18.730Z</t>
+        </is>
+      </c>
+      <c r="L39" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-04T21:47:42Z</t>
+        </is>
+      </c>
+      <c r="M39" s="4" t="n"/>
+      <c r="N39" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>ve_usd_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>USD paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="n">
+        <v>839.457145</v>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>VES por USD</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I40" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K40" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-04T21:01:18.670Z</t>
+        </is>
+      </c>
+      <c r="L40" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-04T21:47:42Z</t>
+        </is>
+      </c>
+      <c r="M40" s="4" t="n"/>
+      <c r="N40" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_compra</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - compra</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>846.5296000000001</v>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I41" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K41" s="4" t="n"/>
+      <c r="L41" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-04T21:47:42Z</t>
+        </is>
+      </c>
+      <c r="M41" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N41" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para compra. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_venta</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - venta</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="n">
+        <v>846.096</v>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I42" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K42" s="4" t="n"/>
+      <c r="L42" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-04T21:47:42Z</t>
+        </is>
+      </c>
+      <c r="M42" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N42" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para venta. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N42"/>
+  <dimension ref="A1:N46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2926,6 +2926,266 @@
         </is>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>ve_eur_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>EUR paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>962.199524</v>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>VES por EUR</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I43" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K43" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:01:32.560Z</t>
+        </is>
+      </c>
+      <c r="L43" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:44:07Z</t>
+        </is>
+      </c>
+      <c r="M43" s="4" t="n"/>
+      <c r="N43" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>ve_usd_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>USD paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="n">
+        <v>832.361282</v>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>VES por USD</t>
+        </is>
+      </c>
+      <c r="G44" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I44" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K44" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:01:32.546Z</t>
+        </is>
+      </c>
+      <c r="L44" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:44:07Z</t>
+        </is>
+      </c>
+      <c r="M44" s="4" t="n"/>
+      <c r="N44" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_compra</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - compra</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="n">
+        <v>846.9401</v>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G45" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H45" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I45" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K45" s="4" t="n"/>
+      <c r="L45" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:44:07Z</t>
+        </is>
+      </c>
+      <c r="M45" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N45" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para compra. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_venta</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - venta</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="n">
+        <v>846.2859</v>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G46" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I46" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K46" s="4" t="n"/>
+      <c r="L46" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:44:07Z</t>
+        </is>
+      </c>
+      <c r="M46" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N46" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para venta. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N46"/>
+  <dimension ref="A1:N50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -3186,6 +3186,266 @@
         </is>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>ve_eur_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>EUR paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="n">
+        <v>962.913239</v>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>VES por EUR</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I47" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K47" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06T20:01:34.256Z</t>
+        </is>
+      </c>
+      <c r="L47" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07T00:56:45Z</t>
+        </is>
+      </c>
+      <c r="M47" s="4" t="n"/>
+      <c r="N47" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>ve_usd_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>USD paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="n">
+        <v>836.153414</v>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>VES por USD</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I48" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K48" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06T20:01:34.194Z</t>
+        </is>
+      </c>
+      <c r="L48" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07T00:56:45Z</t>
+        </is>
+      </c>
+      <c r="M48" s="4" t="n"/>
+      <c r="N48" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_compra</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - compra</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="n">
+        <v>857.067</v>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H49" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I49" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K49" s="4" t="n"/>
+      <c r="L49" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07T00:56:45Z</t>
+        </is>
+      </c>
+      <c r="M49" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N49" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para compra. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_venta</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - venta</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="n">
+        <v>854.3367</v>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I50" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K50" s="4" t="n"/>
+      <c r="L50" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07T00:56:45Z</t>
+        </is>
+      </c>
+      <c r="M50" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N50" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para venta. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -3203,7 +3203,7 @@
         </is>
       </c>
       <c r="D47" s="5" t="n">
-        <v>962.913239</v>
+        <v>977.02417</v>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06T20:01:34.256Z</t>
+          <t>2026-08-07T21:01:10.331Z</t>
         </is>
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:45Z</t>
+          <t>2026-08-07T21:08:56Z</t>
         </is>
       </c>
       <c r="M47" s="4" t="n"/>
@@ -3269,7 +3269,7 @@
         </is>
       </c>
       <c r="D48" s="5" t="n">
-        <v>836.153414</v>
+        <v>845.729708</v>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
@@ -3303,12 +3303,12 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06T20:01:34.194Z</t>
+          <t>2026-08-07T21:01:10.280Z</t>
         </is>
       </c>
       <c r="L48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:45Z</t>
+          <t>2026-08-07T21:08:56Z</t>
         </is>
       </c>
       <c r="M48" s="4" t="n"/>
@@ -3335,7 +3335,7 @@
         </is>
       </c>
       <c r="D49" s="5" t="n">
-        <v>857.067</v>
+        <v>874.53</v>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
       <c r="K49" s="4" t="n"/>
       <c r="L49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:45Z</t>
+          <t>2026-08-07T21:08:56Z</t>
         </is>
       </c>
       <c r="M49" s="6" t="n">
@@ -3399,7 +3399,7 @@
         </is>
       </c>
       <c r="D50" s="5" t="n">
-        <v>854.3367</v>
+        <v>857.2988</v>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
@@ -3434,7 +3434,7 @@
       <c r="K50" s="4" t="n"/>
       <c r="L50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:45Z</t>
+          <t>2026-08-07T21:08:56Z</t>
         </is>
       </c>
       <c r="M50" s="6" t="n">

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N50"/>
+  <dimension ref="A1:N54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -3446,6 +3446,266 @@
         </is>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>ve_eur_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>EUR paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="n">
+        <v>979.04134</v>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>VES por EUR</t>
+        </is>
+      </c>
+      <c r="G51" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H51" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I51" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K51" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-08T18:01:10.327Z</t>
+        </is>
+      </c>
+      <c r="L51" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-08T20:57:37Z</t>
+        </is>
+      </c>
+      <c r="M51" s="4" t="n"/>
+      <c r="N51" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>ve_usd_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>USD paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="n">
+        <v>847.596229</v>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>VES por USD</t>
+        </is>
+      </c>
+      <c r="G52" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H52" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I52" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K52" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-08T18:01:10.298Z</t>
+        </is>
+      </c>
+      <c r="L52" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-08T20:57:37Z</t>
+        </is>
+      </c>
+      <c r="M52" s="4" t="n"/>
+      <c r="N52" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_compra</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - compra</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="n">
+        <v>863.5011</v>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G53" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H53" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I53" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K53" s="4" t="n"/>
+      <c r="L53" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-08T20:57:37Z</t>
+        </is>
+      </c>
+      <c r="M53" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N53" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para compra. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_venta</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - venta</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="n">
+        <v>861.9596</v>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G54" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I54" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K54" s="4" t="n"/>
+      <c r="L54" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-08T20:57:37Z</t>
+        </is>
+      </c>
+      <c r="M54" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N54" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para venta. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N54"/>
+  <dimension ref="A1:N58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -3706,6 +3706,266 @@
         </is>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>ve_eur_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>EUR paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="n">
+        <v>981.8327839999999</v>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>VES por EUR</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H55" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I55" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K55" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-09T18:01:06.867Z</t>
+        </is>
+      </c>
+      <c r="L55" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-09T21:01:49Z</t>
+        </is>
+      </c>
+      <c r="M55" s="4" t="n"/>
+      <c r="N55" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>ve_usd_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>USD paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="n">
+        <v>850.358501</v>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>VES por USD</t>
+        </is>
+      </c>
+      <c r="G56" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I56" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K56" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-09T18:01:06.852Z</t>
+        </is>
+      </c>
+      <c r="L56" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-09T21:01:49Z</t>
+        </is>
+      </c>
+      <c r="M56" s="4" t="n"/>
+      <c r="N56" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_compra</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - compra</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="n">
+        <v>873.198</v>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G57" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H57" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I57" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K57" s="4" t="n"/>
+      <c r="L57" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-09T21:01:49Z</t>
+        </is>
+      </c>
+      <c r="M57" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N57" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para compra. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_venta</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - venta</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="n">
+        <v>863.5896</v>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G58" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I58" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K58" s="4" t="n"/>
+      <c r="L58" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-09T21:01:49Z</t>
+        </is>
+      </c>
+      <c r="M58" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N58" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para venta. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N58"/>
+  <dimension ref="A1:N62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -3966,6 +3966,266 @@
         </is>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>ve_eur_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>EUR paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="n">
+        <v>989.3781739999999</v>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>VES por EUR</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H59" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I59" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K59" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-10T21:01:04.106Z</t>
+        </is>
+      </c>
+      <c r="L59" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-10T21:10:53Z</t>
+        </is>
+      </c>
+      <c r="M59" s="4" t="n"/>
+      <c r="N59" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>ve_usd_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>USD paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="n">
+        <v>857.450531</v>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>VES por USD</t>
+        </is>
+      </c>
+      <c r="G60" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I60" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K60" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-10T21:01:04.095Z</t>
+        </is>
+      </c>
+      <c r="L60" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-10T21:10:53Z</t>
+        </is>
+      </c>
+      <c r="M60" s="4" t="n"/>
+      <c r="N60" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_compra</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - compra</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="n">
+        <v>868.171</v>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G61" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H61" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I61" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K61" s="4" t="n"/>
+      <c r="L61" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-10T21:10:53Z</t>
+        </is>
+      </c>
+      <c r="M61" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N61" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para compra. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_venta</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - venta</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="n">
+        <v>867.5628</v>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G62" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H62" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I62" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K62" s="4" t="n"/>
+      <c r="L62" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-10T21:10:53Z</t>
+        </is>
+      </c>
+      <c r="M62" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N62" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para venta. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N62"/>
+  <dimension ref="A1:N66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -4226,6 +4226,266 @@
         </is>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>ve_eur_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>EUR paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="n">
+        <v>996.661956</v>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>VES por EUR</t>
+        </is>
+      </c>
+      <c r="G63" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H63" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I63" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J63" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K63" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-11T21:01:20.288Z</t>
+        </is>
+      </c>
+      <c r="L63" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-11T21:14:44Z</t>
+        </is>
+      </c>
+      <c r="M63" s="4" t="n"/>
+      <c r="N63" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>ve_usd_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>USD paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="n">
+        <v>863.96439</v>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>VES por USD</t>
+        </is>
+      </c>
+      <c r="G64" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H64" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I64" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K64" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-11T21:01:20.221Z</t>
+        </is>
+      </c>
+      <c r="L64" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-11T21:14:44Z</t>
+        </is>
+      </c>
+      <c r="M64" s="4" t="n"/>
+      <c r="N64" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_compra</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - compra</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="n">
+        <v>875.264</v>
+      </c>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G65" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H65" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I65" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K65" s="4" t="n"/>
+      <c r="L65" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-11T21:14:44Z</t>
+        </is>
+      </c>
+      <c r="M65" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N65" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para compra. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_venta</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - venta</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="n">
+        <v>875.0848999999999</v>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G66" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I66" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K66" s="4" t="n"/>
+      <c r="L66" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-11T21:14:44Z</t>
+        </is>
+      </c>
+      <c r="M66" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N66" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para venta. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N66"/>
+  <dimension ref="A1:N70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -4486,6 +4486,266 @@
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>ve_eur_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>EUR paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="n">
+        <v>996.820408</v>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>VES por EUR</t>
+        </is>
+      </c>
+      <c r="G67" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H67" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I67" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J67" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K67" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-12T21:01:07.323Z</t>
+        </is>
+      </c>
+      <c r="L67" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-12T21:12:34Z</t>
+        </is>
+      </c>
+      <c r="M67" s="4" t="n"/>
+      <c r="N67" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>ve_usd_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>USD paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="D68" s="5" t="n">
+        <v>865.302914</v>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>VES por USD</t>
+        </is>
+      </c>
+      <c r="G68" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I68" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K68" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-12T21:01:07.292Z</t>
+        </is>
+      </c>
+      <c r="L68" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-12T21:12:34Z</t>
+        </is>
+      </c>
+      <c r="M68" s="4" t="n"/>
+      <c r="N68" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_compra</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - compra</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="n">
+        <v>880.4008</v>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G69" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H69" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I69" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J69" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K69" s="4" t="n"/>
+      <c r="L69" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-12T21:12:34Z</t>
+        </is>
+      </c>
+      <c r="M69" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N69" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para compra. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_venta</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - venta</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="D70" s="5" t="n">
+        <v>879.2198</v>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G70" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I70" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K70" s="4" t="n"/>
+      <c r="L70" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-12T21:12:34Z</t>
+        </is>
+      </c>
+      <c r="M70" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N70" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para venta. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N70"/>
+  <dimension ref="A1:N74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -4746,6 +4746,266 @@
         </is>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>ve_eur_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>EUR paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="n">
+        <v>1006.250185</v>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>VES por EUR</t>
+        </is>
+      </c>
+      <c r="G71" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H71" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I71" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J71" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K71" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-13T21:01:10.186Z</t>
+        </is>
+      </c>
+      <c r="L71" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-13T21:12:19Z</t>
+        </is>
+      </c>
+      <c r="M71" s="4" t="n"/>
+      <c r="N71" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>ve_usd_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>USD paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="n">
+        <v>873.124292</v>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>VES por USD</t>
+        </is>
+      </c>
+      <c r="G72" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I72" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K72" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-13T21:01:10.111Z</t>
+        </is>
+      </c>
+      <c r="L72" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-13T21:12:19Z</t>
+        </is>
+      </c>
+      <c r="M72" s="4" t="n"/>
+      <c r="N72" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_compra</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - compra</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="n">
+        <v>892.6349</v>
+      </c>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G73" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H73" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I73" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K73" s="4" t="n"/>
+      <c r="L73" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-13T21:12:19Z</t>
+        </is>
+      </c>
+      <c r="M73" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N73" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para compra. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_venta</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - venta</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="D74" s="5" t="n">
+        <v>889.936</v>
+      </c>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G74" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H74" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I74" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K74" s="4" t="n"/>
+      <c r="L74" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-13T21:12:19Z</t>
+        </is>
+      </c>
+      <c r="M74" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N74" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para venta. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N74"/>
+  <dimension ref="A1:N78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -5006,6 +5006,266 @@
         </is>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>ve_eur_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>EUR paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="n">
+        <v>1012.249627</v>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t>VES por EUR</t>
+        </is>
+      </c>
+      <c r="G75" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H75" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I75" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J75" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K75" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-14T20:01:36.348Z</t>
+        </is>
+      </c>
+      <c r="L75" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-14T20:54:57Z</t>
+        </is>
+      </c>
+      <c r="M75" s="4" t="n"/>
+      <c r="N75" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>ve_usd_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t>USD paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="D76" s="5" t="n">
+        <v>875.342865</v>
+      </c>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F76" s="4" t="inlineStr">
+        <is>
+          <t>VES por USD</t>
+        </is>
+      </c>
+      <c r="G76" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H76" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I76" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K76" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-14T20:01:36.285Z</t>
+        </is>
+      </c>
+      <c r="L76" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-14T20:54:57Z</t>
+        </is>
+      </c>
+      <c r="M76" s="4" t="n"/>
+      <c r="N76" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_compra</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - compra</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="n">
+        <v>884.6610000000001</v>
+      </c>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F77" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G77" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H77" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I77" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J77" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K77" s="4" t="n"/>
+      <c r="L77" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-14T20:54:57Z</t>
+        </is>
+      </c>
+      <c r="M77" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N77" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para compra. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_venta</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - venta</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="D78" s="5" t="n">
+        <v>883.2968</v>
+      </c>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F78" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G78" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H78" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I78" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K78" s="4" t="n"/>
+      <c r="L78" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-14T20:54:57Z</t>
+        </is>
+      </c>
+      <c r="M78" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N78" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para venta. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N78"/>
+  <dimension ref="A1:N82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -5266,6 +5266,266 @@
         </is>
       </c>
     </row>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>ve_eur_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>EUR paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="D79" s="5" t="n">
+        <v>987.862856</v>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>VES por EUR</t>
+        </is>
+      </c>
+      <c r="G79" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H79" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I79" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J79" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K79" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-15T18:01:03.525Z</t>
+        </is>
+      </c>
+      <c r="L79" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-15T20:46:54Z</t>
+        </is>
+      </c>
+      <c r="M79" s="4" t="n"/>
+      <c r="N79" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>ve_usd_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>USD paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="D80" s="5" t="n">
+        <v>854.560642</v>
+      </c>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F80" s="4" t="inlineStr">
+        <is>
+          <t>VES por USD</t>
+        </is>
+      </c>
+      <c r="G80" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H80" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I80" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K80" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-15T18:01:03.515Z</t>
+        </is>
+      </c>
+      <c r="L80" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-15T20:46:54Z</t>
+        </is>
+      </c>
+      <c r="M80" s="4" t="n"/>
+      <c r="N80" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_compra</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - compra</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="n">
+        <v>873.3057</v>
+      </c>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F81" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G81" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H81" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I81" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J81" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K81" s="4" t="n"/>
+      <c r="L81" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-15T20:46:54Z</t>
+        </is>
+      </c>
+      <c r="M81" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N81" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para compra. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_venta</t>
+        </is>
+      </c>
+      <c r="B82" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - venta</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="D82" s="5" t="n">
+        <v>872.4829</v>
+      </c>
+      <c r="E82" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F82" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G82" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H82" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I82" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K82" s="4" t="n"/>
+      <c r="L82" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-15T20:46:54Z</t>
+        </is>
+      </c>
+      <c r="M82" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N82" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para venta. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N82"/>
+  <dimension ref="A1:N86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -5526,6 +5526,266 @@
         </is>
       </c>
     </row>
+    <row r="83">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t>ve_eur_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>EUR paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="D83" s="5" t="n">
+        <v>981.502347</v>
+      </c>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F83" s="4" t="inlineStr">
+        <is>
+          <t>VES por EUR</t>
+        </is>
+      </c>
+      <c r="G83" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H83" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I83" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J83" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K83" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-16T18:01:16.490Z</t>
+        </is>
+      </c>
+      <c r="L83" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-16T20:45:54Z</t>
+        </is>
+      </c>
+      <c r="M83" s="4" t="n"/>
+      <c r="N83" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="4" t="inlineStr">
+        <is>
+          <t>ve_usd_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t>USD paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="D84" s="5" t="n">
+        <v>849.18896</v>
+      </c>
+      <c r="E84" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F84" s="4" t="inlineStr">
+        <is>
+          <t>VES por USD</t>
+        </is>
+      </c>
+      <c r="G84" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H84" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I84" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K84" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-16T18:01:16.453Z</t>
+        </is>
+      </c>
+      <c r="L84" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-16T20:45:54Z</t>
+        </is>
+      </c>
+      <c r="M84" s="4" t="n"/>
+      <c r="N84" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_compra</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - compra</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="D85" s="5" t="n">
+        <v>869.317</v>
+      </c>
+      <c r="E85" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F85" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G85" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H85" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I85" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J85" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K85" s="4" t="n"/>
+      <c r="L85" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-16T20:45:54Z</t>
+        </is>
+      </c>
+      <c r="M85" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N85" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para compra. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_venta</t>
+        </is>
+      </c>
+      <c r="B86" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - venta</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="D86" s="5" t="n">
+        <v>862.8282</v>
+      </c>
+      <c r="E86" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F86" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G86" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H86" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I86" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J86" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K86" s="4" t="n"/>
+      <c r="L86" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-16T20:45:54Z</t>
+        </is>
+      </c>
+      <c r="M86" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N86" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para venta. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N86"/>
+  <dimension ref="A1:N90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -5786,6 +5786,266 @@
         </is>
       </c>
     </row>
+    <row r="87">
+      <c r="A87" s="4" t="inlineStr">
+        <is>
+          <t>ve_eur_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>EUR paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="D87" s="5" t="n">
+        <v>1006.613819</v>
+      </c>
+      <c r="E87" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F87" s="4" t="inlineStr">
+        <is>
+          <t>VES por EUR</t>
+        </is>
+      </c>
+      <c r="G87" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H87" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I87" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J87" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K87" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-17T20:01:50.404Z</t>
+        </is>
+      </c>
+      <c r="L87" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-17T20:52:36Z</t>
+        </is>
+      </c>
+      <c r="M87" s="4" t="n"/>
+      <c r="N87" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="4" t="inlineStr">
+        <is>
+          <t>ve_usd_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B88" s="4" t="inlineStr">
+        <is>
+          <t>USD paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C88" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="D88" s="5" t="n">
+        <v>869.656963</v>
+      </c>
+      <c r="E88" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F88" s="4" t="inlineStr">
+        <is>
+          <t>VES por USD</t>
+        </is>
+      </c>
+      <c r="G88" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H88" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I88" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J88" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K88" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-17T20:01:50.338Z</t>
+        </is>
+      </c>
+      <c r="L88" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-17T20:52:36Z</t>
+        </is>
+      </c>
+      <c r="M88" s="4" t="n"/>
+      <c r="N88" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_compra</t>
+        </is>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - compra</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="D89" s="5" t="n">
+        <v>888.114</v>
+      </c>
+      <c r="E89" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F89" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G89" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H89" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I89" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J89" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K89" s="4" t="n"/>
+      <c r="L89" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-17T20:52:36Z</t>
+        </is>
+      </c>
+      <c r="M89" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N89" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para compra. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_venta</t>
+        </is>
+      </c>
+      <c r="B90" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - venta</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="D90" s="5" t="n">
+        <v>884.9999</v>
+      </c>
+      <c r="E90" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F90" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G90" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H90" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I90" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J90" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K90" s="4" t="n"/>
+      <c r="L90" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-17T20:52:36Z</t>
+        </is>
+      </c>
+      <c r="M90" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N90" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para venta. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N90"/>
+  <dimension ref="A1:N94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -6046,6 +6046,266 @@
         </is>
       </c>
     </row>
+    <row r="91">
+      <c r="A91" s="4" t="inlineStr">
+        <is>
+          <t>ve_eur_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t>EUR paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D91" s="5" t="n">
+        <v>1050.546236</v>
+      </c>
+      <c r="E91" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F91" s="4" t="inlineStr">
+        <is>
+          <t>VES por EUR</t>
+        </is>
+      </c>
+      <c r="G91" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H91" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I91" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J91" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K91" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-21T16:01:00.070Z</t>
+        </is>
+      </c>
+      <c r="L91" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-21T16:34:10Z</t>
+        </is>
+      </c>
+      <c r="M91" s="4" t="n"/>
+      <c r="N91" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t>ve_usd_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B92" s="4" t="inlineStr">
+        <is>
+          <t>USD paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D92" s="5" t="n">
+        <v>899.621612</v>
+      </c>
+      <c r="E92" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F92" s="4" t="inlineStr">
+        <is>
+          <t>VES por USD</t>
+        </is>
+      </c>
+      <c r="G92" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H92" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I92" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J92" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K92" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-21T16:01:00.059Z</t>
+        </is>
+      </c>
+      <c r="L92" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-21T16:34:10Z</t>
+        </is>
+      </c>
+      <c r="M92" s="4" t="n"/>
+      <c r="N92" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_compra</t>
+        </is>
+      </c>
+      <c r="B93" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - compra</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D93" s="5" t="n">
+        <v>918.5741</v>
+      </c>
+      <c r="E93" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F93" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G93" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H93" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I93" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J93" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K93" s="4" t="n"/>
+      <c r="L93" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-21T16:34:10Z</t>
+        </is>
+      </c>
+      <c r="M93" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N93" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para compra. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_venta</t>
+        </is>
+      </c>
+      <c r="B94" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - venta</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D94" s="5" t="n">
+        <v>919.1799</v>
+      </c>
+      <c r="E94" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F94" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G94" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H94" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I94" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J94" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K94" s="4" t="n"/>
+      <c r="L94" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-21T16:34:10Z</t>
+        </is>
+      </c>
+      <c r="M94" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N94" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para venta. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -6063,7 +6063,7 @@
         </is>
       </c>
       <c r="D91" s="5" t="n">
-        <v>1050.546236</v>
+        <v>1049.443694</v>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
@@ -6097,12 +6097,12 @@
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:01:00.070Z</t>
+          <t>2026-08-21T20:02:07.719Z</t>
         </is>
       </c>
       <c r="L91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:10Z</t>
+          <t>2026-08-21T20:49:21Z</t>
         </is>
       </c>
       <c r="M91" s="4" t="n"/>
@@ -6129,7 +6129,7 @@
         </is>
       </c>
       <c r="D92" s="5" t="n">
-        <v>899.621612</v>
+        <v>898.749876</v>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
@@ -6163,12 +6163,12 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:01:00.059Z</t>
+          <t>2026-08-21T20:02:07.644Z</t>
         </is>
       </c>
       <c r="L92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:10Z</t>
+          <t>2026-08-21T20:49:21Z</t>
         </is>
       </c>
       <c r="M92" s="4" t="n"/>
@@ -6195,7 +6195,7 @@
         </is>
       </c>
       <c r="D93" s="5" t="n">
-        <v>918.5741</v>
+        <v>917.6545</v>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
@@ -6230,7 +6230,7 @@
       <c r="K93" s="4" t="n"/>
       <c r="L93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:10Z</t>
+          <t>2026-08-21T20:49:21Z</t>
         </is>
       </c>
       <c r="M93" s="6" t="n">
@@ -6259,7 +6259,7 @@
         </is>
       </c>
       <c r="D94" s="5" t="n">
-        <v>919.1799</v>
+        <v>918.7578</v>
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
@@ -6294,7 +6294,7 @@
       <c r="K94" s="4" t="n"/>
       <c r="L94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:10Z</t>
+          <t>2026-08-21T20:49:21Z</t>
         </is>
       </c>
       <c r="M94" s="6" t="n">

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N94"/>
+  <dimension ref="A1:N98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -6306,6 +6306,266 @@
         </is>
       </c>
     </row>
+    <row r="95">
+      <c r="A95" s="4" t="inlineStr">
+        <is>
+          <t>ve_eur_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>EUR paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="D95" s="5" t="n">
+        <v>1054.738219</v>
+      </c>
+      <c r="E95" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F95" s="4" t="inlineStr">
+        <is>
+          <t>VES por EUR</t>
+        </is>
+      </c>
+      <c r="G95" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H95" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I95" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J95" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K95" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-22T18:01:02.039Z</t>
+        </is>
+      </c>
+      <c r="L95" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-22T20:47:33Z</t>
+        </is>
+      </c>
+      <c r="M95" s="4" t="n"/>
+      <c r="N95" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t>ve_usd_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B96" s="4" t="inlineStr">
+        <is>
+          <t>USD paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="D96" s="5" t="n">
+        <v>900.886719</v>
+      </c>
+      <c r="E96" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F96" s="4" t="inlineStr">
+        <is>
+          <t>VES por USD</t>
+        </is>
+      </c>
+      <c r="G96" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H96" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I96" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J96" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K96" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-22T18:01:02.028Z</t>
+        </is>
+      </c>
+      <c r="L96" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-22T20:47:33Z</t>
+        </is>
+      </c>
+      <c r="M96" s="4" t="n"/>
+      <c r="N96" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_compra</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - compra</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="D97" s="5" t="n">
+        <v>918.8161</v>
+      </c>
+      <c r="E97" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F97" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G97" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H97" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I97" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J97" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K97" s="4" t="n"/>
+      <c r="L97" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-22T20:47:33Z</t>
+        </is>
+      </c>
+      <c r="M97" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N97" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para compra. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_venta</t>
+        </is>
+      </c>
+      <c r="B98" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - venta</t>
+        </is>
+      </c>
+      <c r="C98" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="D98" s="5" t="n">
+        <v>919.6693</v>
+      </c>
+      <c r="E98" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F98" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G98" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H98" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I98" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J98" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K98" s="4" t="n"/>
+      <c r="L98" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-22T20:47:33Z</t>
+        </is>
+      </c>
+      <c r="M98" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N98" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para venta. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N98"/>
+  <dimension ref="A1:N102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -6566,6 +6566,266 @@
         </is>
       </c>
     </row>
+    <row r="99">
+      <c r="A99" s="4" t="inlineStr">
+        <is>
+          <t>ve_eur_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B99" s="4" t="inlineStr">
+        <is>
+          <t>EUR paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C99" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="D99" s="5" t="n">
+        <v>1047.76003</v>
+      </c>
+      <c r="E99" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F99" s="4" t="inlineStr">
+        <is>
+          <t>VES por EUR</t>
+        </is>
+      </c>
+      <c r="G99" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H99" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I99" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J99" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K99" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-23T18:01:16.976Z</t>
+        </is>
+      </c>
+      <c r="L99" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-23T20:47:17Z</t>
+        </is>
+      </c>
+      <c r="M99" s="4" t="n"/>
+      <c r="N99" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="4" t="inlineStr">
+        <is>
+          <t>ve_usd_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B100" s="4" t="inlineStr">
+        <is>
+          <t>USD paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C100" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="D100" s="5" t="n">
+        <v>895.46811</v>
+      </c>
+      <c r="E100" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F100" s="4" t="inlineStr">
+        <is>
+          <t>VES por USD</t>
+        </is>
+      </c>
+      <c r="G100" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H100" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I100" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J100" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K100" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-23T18:01:16.903Z</t>
+        </is>
+      </c>
+      <c r="L100" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-23T20:47:17Z</t>
+        </is>
+      </c>
+      <c r="M100" s="4" t="n"/>
+      <c r="N100" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_compra</t>
+        </is>
+      </c>
+      <c r="B101" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - compra</t>
+        </is>
+      </c>
+      <c r="C101" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="D101" s="5" t="n">
+        <v>921.6718000000001</v>
+      </c>
+      <c r="E101" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F101" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G101" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H101" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I101" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J101" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K101" s="4" t="n"/>
+      <c r="L101" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-23T20:47:17Z</t>
+        </is>
+      </c>
+      <c r="M101" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N101" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para compra. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_venta</t>
+        </is>
+      </c>
+      <c r="B102" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - venta</t>
+        </is>
+      </c>
+      <c r="C102" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="D102" s="5" t="n">
+        <v>919.7996000000001</v>
+      </c>
+      <c r="E102" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F102" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G102" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H102" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I102" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J102" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K102" s="4" t="n"/>
+      <c r="L102" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-23T20:47:17Z</t>
+        </is>
+      </c>
+      <c r="M102" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N102" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para venta. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N102"/>
+  <dimension ref="A1:N106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -6826,6 +6826,266 @@
         </is>
       </c>
     </row>
+    <row r="103">
+      <c r="A103" s="4" t="inlineStr">
+        <is>
+          <t>ve_eur_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B103" s="4" t="inlineStr">
+        <is>
+          <t>EUR paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C103" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="D103" s="5" t="n">
+        <v>1065.01016</v>
+      </c>
+      <c r="E103" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F103" s="4" t="inlineStr">
+        <is>
+          <t>VES por EUR</t>
+        </is>
+      </c>
+      <c r="G103" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H103" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I103" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J103" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K103" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-24T20:01:33.450Z</t>
+        </is>
+      </c>
+      <c r="L103" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-24T20:57:33Z</t>
+        </is>
+      </c>
+      <c r="M103" s="4" t="n"/>
+      <c r="N103" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="4" t="inlineStr">
+        <is>
+          <t>ve_usd_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B104" s="4" t="inlineStr">
+        <is>
+          <t>USD paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C104" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="D104" s="5" t="n">
+        <v>914.527419</v>
+      </c>
+      <c r="E104" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F104" s="4" t="inlineStr">
+        <is>
+          <t>VES por USD</t>
+        </is>
+      </c>
+      <c r="G104" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H104" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I104" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J104" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K104" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-24T20:01:33.439Z</t>
+        </is>
+      </c>
+      <c r="L104" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-24T20:57:33Z</t>
+        </is>
+      </c>
+      <c r="M104" s="4" t="n"/>
+      <c r="N104" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_compra</t>
+        </is>
+      </c>
+      <c r="B105" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - compra</t>
+        </is>
+      </c>
+      <c r="C105" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="D105" s="5" t="n">
+        <v>931.4517</v>
+      </c>
+      <c r="E105" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F105" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G105" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H105" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I105" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J105" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K105" s="4" t="n"/>
+      <c r="L105" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-24T20:57:33Z</t>
+        </is>
+      </c>
+      <c r="M105" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N105" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para compra. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_venta</t>
+        </is>
+      </c>
+      <c r="B106" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - venta</t>
+        </is>
+      </c>
+      <c r="C106" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="D106" s="5" t="n">
+        <v>931.1096</v>
+      </c>
+      <c r="E106" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F106" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G106" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H106" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I106" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J106" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K106" s="4" t="n"/>
+      <c r="L106" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-24T20:57:33Z</t>
+        </is>
+      </c>
+      <c r="M106" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N106" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para venta. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N106"/>
+  <dimension ref="A1:N110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -7086,6 +7086,266 @@
         </is>
       </c>
     </row>
+    <row r="107">
+      <c r="A107" s="4" t="inlineStr">
+        <is>
+          <t>ve_eur_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B107" s="4" t="inlineStr">
+        <is>
+          <t>EUR paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C107" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="D107" s="5" t="n">
+        <v>1070.352153</v>
+      </c>
+      <c r="E107" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F107" s="4" t="inlineStr">
+        <is>
+          <t>VES por EUR</t>
+        </is>
+      </c>
+      <c r="G107" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H107" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I107" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J107" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K107" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-25T20:02:21.936Z</t>
+        </is>
+      </c>
+      <c r="L107" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-25T20:54:47Z</t>
+        </is>
+      </c>
+      <c r="M107" s="4" t="n"/>
+      <c r="N107" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="4" t="inlineStr">
+        <is>
+          <t>ve_usd_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B108" s="4" t="inlineStr">
+        <is>
+          <t>USD paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C108" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="D108" s="5" t="n">
+        <v>917.433082</v>
+      </c>
+      <c r="E108" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F108" s="4" t="inlineStr">
+        <is>
+          <t>VES por USD</t>
+        </is>
+      </c>
+      <c r="G108" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H108" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I108" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J108" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K108" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-25T20:02:21.926Z</t>
+        </is>
+      </c>
+      <c r="L108" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-25T20:54:47Z</t>
+        </is>
+      </c>
+      <c r="M108" s="4" t="n"/>
+      <c r="N108" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_compra</t>
+        </is>
+      </c>
+      <c r="B109" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - compra</t>
+        </is>
+      </c>
+      <c r="C109" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="D109" s="5" t="n">
+        <v>935.61</v>
+      </c>
+      <c r="E109" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F109" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G109" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H109" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I109" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J109" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K109" s="4" t="n"/>
+      <c r="L109" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-25T20:54:47Z</t>
+        </is>
+      </c>
+      <c r="M109" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N109" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para compra. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_venta</t>
+        </is>
+      </c>
+      <c r="B110" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - venta</t>
+        </is>
+      </c>
+      <c r="C110" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="D110" s="5" t="n">
+        <v>935.365</v>
+      </c>
+      <c r="E110" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F110" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G110" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H110" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I110" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J110" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K110" s="4" t="n"/>
+      <c r="L110" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-25T20:54:47Z</t>
+        </is>
+      </c>
+      <c r="M110" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N110" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para venta. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N110"/>
+  <dimension ref="A1:N114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -7346,6 +7346,266 @@
         </is>
       </c>
     </row>
+    <row r="111">
+      <c r="A111" s="4" t="inlineStr">
+        <is>
+          <t>ve_eur_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B111" s="4" t="inlineStr">
+        <is>
+          <t>EUR paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C111" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="D111" s="5" t="n">
+        <v>1084.323936</v>
+      </c>
+      <c r="E111" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F111" s="4" t="inlineStr">
+        <is>
+          <t>VES por EUR</t>
+        </is>
+      </c>
+      <c r="G111" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H111" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I111" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J111" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K111" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-26T21:01:38.716Z</t>
+        </is>
+      </c>
+      <c r="L111" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-26T23:55:33Z</t>
+        </is>
+      </c>
+      <c r="M111" s="4" t="n"/>
+      <c r="N111" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="4" t="inlineStr">
+        <is>
+          <t>ve_usd_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B112" s="4" t="inlineStr">
+        <is>
+          <t>USD paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C112" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="D112" s="5" t="n">
+        <v>931.282456</v>
+      </c>
+      <c r="E112" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F112" s="4" t="inlineStr">
+        <is>
+          <t>VES por USD</t>
+        </is>
+      </c>
+      <c r="G112" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H112" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I112" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J112" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K112" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-26T21:01:38.705Z</t>
+        </is>
+      </c>
+      <c r="L112" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-26T23:55:33Z</t>
+        </is>
+      </c>
+      <c r="M112" s="4" t="n"/>
+      <c r="N112" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_compra</t>
+        </is>
+      </c>
+      <c r="B113" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - compra</t>
+        </is>
+      </c>
+      <c r="C113" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="D113" s="5" t="n">
+        <v>952.9864</v>
+      </c>
+      <c r="E113" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F113" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G113" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H113" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I113" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J113" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K113" s="4" t="n"/>
+      <c r="L113" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-26T23:55:33Z</t>
+        </is>
+      </c>
+      <c r="M113" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N113" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para compra. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_venta</t>
+        </is>
+      </c>
+      <c r="B114" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - venta</t>
+        </is>
+      </c>
+      <c r="C114" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="D114" s="5" t="n">
+        <v>954.0948</v>
+      </c>
+      <c r="E114" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F114" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G114" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H114" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I114" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J114" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K114" s="4" t="n"/>
+      <c r="L114" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-26T23:55:33Z</t>
+        </is>
+      </c>
+      <c r="M114" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N114" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para venta. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N114"/>
+  <dimension ref="A1:N118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -7606,6 +7606,266 @@
         </is>
       </c>
     </row>
+    <row r="115">
+      <c r="A115" s="4" t="inlineStr">
+        <is>
+          <t>ve_eur_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B115" s="4" t="inlineStr">
+        <is>
+          <t>EUR paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C115" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="D115" s="5" t="n">
+        <v>1085.805099</v>
+      </c>
+      <c r="E115" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F115" s="4" t="inlineStr">
+        <is>
+          <t>VES por EUR</t>
+        </is>
+      </c>
+      <c r="G115" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H115" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I115" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J115" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K115" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-28T04:01:54.078Z</t>
+        </is>
+      </c>
+      <c r="L115" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-28T04:24:51Z</t>
+        </is>
+      </c>
+      <c r="M115" s="4" t="n"/>
+      <c r="N115" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="4" t="inlineStr">
+        <is>
+          <t>ve_usd_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B116" s="4" t="inlineStr">
+        <is>
+          <t>USD paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C116" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="D116" s="5" t="n">
+        <v>932.9530580000001</v>
+      </c>
+      <c r="E116" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F116" s="4" t="inlineStr">
+        <is>
+          <t>VES por USD</t>
+        </is>
+      </c>
+      <c r="G116" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H116" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I116" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J116" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K116" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-28T04:01:54.063Z</t>
+        </is>
+      </c>
+      <c r="L116" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-28T04:24:51Z</t>
+        </is>
+      </c>
+      <c r="M116" s="4" t="n"/>
+      <c r="N116" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_compra</t>
+        </is>
+      </c>
+      <c r="B117" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - compra</t>
+        </is>
+      </c>
+      <c r="C117" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="D117" s="5" t="n">
+        <v>939.1279</v>
+      </c>
+      <c r="E117" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F117" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G117" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H117" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I117" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J117" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K117" s="4" t="n"/>
+      <c r="L117" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-28T04:24:51Z</t>
+        </is>
+      </c>
+      <c r="M117" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N117" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para compra. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_venta</t>
+        </is>
+      </c>
+      <c r="B118" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - venta</t>
+        </is>
+      </c>
+      <c r="C118" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="D118" s="5" t="n">
+        <v>939.694</v>
+      </c>
+      <c r="E118" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F118" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G118" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H118" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I118" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J118" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K118" s="4" t="n"/>
+      <c r="L118" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-28T04:24:51Z</t>
+        </is>
+      </c>
+      <c r="M118" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N118" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para venta. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N118"/>
+  <dimension ref="A1:N122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -7866,6 +7866,266 @@
         </is>
       </c>
     </row>
+    <row r="119">
+      <c r="A119" s="4" t="inlineStr">
+        <is>
+          <t>ve_eur_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B119" s="4" t="inlineStr">
+        <is>
+          <t>EUR paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C119" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="D119" s="5" t="n">
+        <v>1067.199688</v>
+      </c>
+      <c r="E119" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F119" s="4" t="inlineStr">
+        <is>
+          <t>VES por EUR</t>
+        </is>
+      </c>
+      <c r="G119" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H119" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I119" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J119" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K119" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-28T21:01:01.950Z</t>
+        </is>
+      </c>
+      <c r="L119" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-29T02:52:39Z</t>
+        </is>
+      </c>
+      <c r="M119" s="4" t="n"/>
+      <c r="N119" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="4" t="inlineStr">
+        <is>
+          <t>ve_usd_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B120" s="4" t="inlineStr">
+        <is>
+          <t>USD paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C120" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="D120" s="5" t="n">
+        <v>922.19393</v>
+      </c>
+      <c r="E120" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F120" s="4" t="inlineStr">
+        <is>
+          <t>VES por USD</t>
+        </is>
+      </c>
+      <c r="G120" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H120" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I120" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J120" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K120" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-28T21:01:01.939Z</t>
+        </is>
+      </c>
+      <c r="L120" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-29T02:52:39Z</t>
+        </is>
+      </c>
+      <c r="M120" s="4" t="n"/>
+      <c r="N120" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_compra</t>
+        </is>
+      </c>
+      <c r="B121" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - compra</t>
+        </is>
+      </c>
+      <c r="C121" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="D121" s="5" t="n">
+        <v>941.4846</v>
+      </c>
+      <c r="E121" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F121" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G121" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H121" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I121" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J121" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K121" s="4" t="n"/>
+      <c r="L121" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-29T02:52:39Z</t>
+        </is>
+      </c>
+      <c r="M121" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N121" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para compra. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_venta</t>
+        </is>
+      </c>
+      <c r="B122" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - venta</t>
+        </is>
+      </c>
+      <c r="C122" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="D122" s="5" t="n">
+        <v>941.0636</v>
+      </c>
+      <c r="E122" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F122" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G122" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H122" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I122" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J122" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K122" s="4" t="n"/>
+      <c r="L122" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-29T02:52:39Z</t>
+        </is>
+      </c>
+      <c r="M122" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N122" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para venta. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -7883,7 +7883,7 @@
         </is>
       </c>
       <c r="D119" s="5" t="n">
-        <v>1067.199688</v>
+        <v>1066.975915</v>
       </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
@@ -7917,12 +7917,12 @@
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T21:01:01.950Z</t>
+          <t>2026-08-29T21:00:59.007Z</t>
         </is>
       </c>
       <c r="L119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:39Z</t>
+          <t>2026-08-29T22:42:58Z</t>
         </is>
       </c>
       <c r="M119" s="4" t="n"/>
@@ -7949,7 +7949,7 @@
         </is>
       </c>
       <c r="D120" s="5" t="n">
-        <v>922.19393</v>
+        <v>922.2352969999999</v>
       </c>
       <c r="E120" s="4" t="inlineStr">
         <is>
@@ -7983,12 +7983,12 @@
       </c>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28T21:01:01.939Z</t>
+          <t>2026-08-29T21:00:58.996Z</t>
         </is>
       </c>
       <c r="L120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:39Z</t>
+          <t>2026-08-29T22:42:58Z</t>
         </is>
       </c>
       <c r="M120" s="4" t="n"/>
@@ -8015,7 +8015,7 @@
         </is>
       </c>
       <c r="D121" s="5" t="n">
-        <v>941.4846</v>
+        <v>936.2945</v>
       </c>
       <c r="E121" s="4" t="inlineStr">
         <is>
@@ -8050,7 +8050,7 @@
       <c r="K121" s="4" t="n"/>
       <c r="L121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:39Z</t>
+          <t>2026-08-29T22:42:58Z</t>
         </is>
       </c>
       <c r="M121" s="6" t="n">
@@ -8079,7 +8079,7 @@
         </is>
       </c>
       <c r="D122" s="5" t="n">
-        <v>941.0636</v>
+        <v>936.8516</v>
       </c>
       <c r="E122" s="4" t="inlineStr">
         <is>
@@ -8114,7 +8114,7 @@
       <c r="K122" s="4" t="n"/>
       <c r="L122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:39Z</t>
+          <t>2026-08-29T22:42:58Z</t>
         </is>
       </c>
       <c r="M122" s="6" t="n">

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N122"/>
+  <dimension ref="A1:N126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -8126,6 +8126,266 @@
         </is>
       </c>
     </row>
+    <row r="123">
+      <c r="A123" s="4" t="inlineStr">
+        <is>
+          <t>ve_eur_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B123" s="4" t="inlineStr">
+        <is>
+          <t>EUR paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C123" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="D123" s="5" t="n">
+        <v>1068.431526</v>
+      </c>
+      <c r="E123" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F123" s="4" t="inlineStr">
+        <is>
+          <t>VES por EUR</t>
+        </is>
+      </c>
+      <c r="G123" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H123" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I123" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J123" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K123" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-30T21:01:28.332Z</t>
+        </is>
+      </c>
+      <c r="L123" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-30T22:52:36Z</t>
+        </is>
+      </c>
+      <c r="M123" s="4" t="n"/>
+      <c r="N123" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="4" t="inlineStr">
+        <is>
+          <t>ve_usd_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B124" s="4" t="inlineStr">
+        <is>
+          <t>USD paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C124" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="D124" s="5" t="n">
+        <v>922.972053</v>
+      </c>
+      <c r="E124" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F124" s="4" t="inlineStr">
+        <is>
+          <t>VES por USD</t>
+        </is>
+      </c>
+      <c r="G124" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H124" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I124" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J124" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K124" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-30T21:01:28.275Z</t>
+        </is>
+      </c>
+      <c r="L124" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-30T22:52:36Z</t>
+        </is>
+      </c>
+      <c r="M124" s="4" t="n"/>
+      <c r="N124" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_compra</t>
+        </is>
+      </c>
+      <c r="B125" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - compra</t>
+        </is>
+      </c>
+      <c r="C125" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="D125" s="5" t="n">
+        <v>933.702</v>
+      </c>
+      <c r="E125" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F125" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G125" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H125" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I125" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J125" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K125" s="4" t="n"/>
+      <c r="L125" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-30T22:52:36Z</t>
+        </is>
+      </c>
+      <c r="M125" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N125" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para compra. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_venta</t>
+        </is>
+      </c>
+      <c r="B126" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - venta</t>
+        </is>
+      </c>
+      <c r="C126" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="D126" s="5" t="n">
+        <v>935.2346</v>
+      </c>
+      <c r="E126" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F126" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G126" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H126" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I126" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J126" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K126" s="4" t="n"/>
+      <c r="L126" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-30T22:52:36Z</t>
+        </is>
+      </c>
+      <c r="M126" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N126" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para venta. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N126"/>
+  <dimension ref="A1:N130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -8386,6 +8386,266 @@
         </is>
       </c>
     </row>
+    <row r="127">
+      <c r="A127" s="4" t="inlineStr">
+        <is>
+          <t>ve_eur_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B127" s="4" t="inlineStr">
+        <is>
+          <t>EUR paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C127" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="D127" s="5" t="n">
+        <v>1070.832195</v>
+      </c>
+      <c r="E127" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F127" s="4" t="inlineStr">
+        <is>
+          <t>VES por EUR</t>
+        </is>
+      </c>
+      <c r="G127" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H127" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I127" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J127" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K127" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-31T21:01:06.764Z</t>
+        </is>
+      </c>
+      <c r="L127" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-31T23:58:29Z</t>
+        </is>
+      </c>
+      <c r="M127" s="4" t="n"/>
+      <c r="N127" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="4" t="inlineStr">
+        <is>
+          <t>ve_usd_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B128" s="4" t="inlineStr">
+        <is>
+          <t>USD paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C128" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="D128" s="5" t="n">
+        <v>922.377374</v>
+      </c>
+      <c r="E128" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F128" s="4" t="inlineStr">
+        <is>
+          <t>VES por USD</t>
+        </is>
+      </c>
+      <c r="G128" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H128" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I128" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J128" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K128" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-31T21:01:06.717Z</t>
+        </is>
+      </c>
+      <c r="L128" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-31T23:58:29Z</t>
+        </is>
+      </c>
+      <c r="M128" s="4" t="n"/>
+      <c r="N128" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_compra</t>
+        </is>
+      </c>
+      <c r="B129" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - compra</t>
+        </is>
+      </c>
+      <c r="C129" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="D129" s="5" t="n">
+        <v>937.4062</v>
+      </c>
+      <c r="E129" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F129" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G129" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H129" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I129" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J129" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K129" s="4" t="n"/>
+      <c r="L129" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-31T23:58:29Z</t>
+        </is>
+      </c>
+      <c r="M129" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N129" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para compra. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_venta</t>
+        </is>
+      </c>
+      <c r="B130" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - venta</t>
+        </is>
+      </c>
+      <c r="C130" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="D130" s="5" t="n">
+        <v>934.756</v>
+      </c>
+      <c r="E130" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F130" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G130" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H130" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I130" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J130" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K130" s="4" t="n"/>
+      <c r="L130" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-31T23:58:29Z</t>
+        </is>
+      </c>
+      <c r="M130" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N130" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para venta. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N130"/>
+  <dimension ref="A1:N134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -8646,6 +8646,266 @@
         </is>
       </c>
     </row>
+    <row r="131">
+      <c r="A131" s="4" t="inlineStr">
+        <is>
+          <t>ve_eur_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B131" s="4" t="inlineStr">
+        <is>
+          <t>EUR paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C131" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="D131" s="5" t="n">
+        <v>1091.977898</v>
+      </c>
+      <c r="E131" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F131" s="4" t="inlineStr">
+        <is>
+          <t>VES por EUR</t>
+        </is>
+      </c>
+      <c r="G131" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H131" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I131" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J131" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K131" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01T21:01:21.734Z</t>
+        </is>
+      </c>
+      <c r="L131" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01T22:43:05Z</t>
+        </is>
+      </c>
+      <c r="M131" s="4" t="n"/>
+      <c r="N131" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="4" t="inlineStr">
+        <is>
+          <t>ve_usd_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B132" s="4" t="inlineStr">
+        <is>
+          <t>USD paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C132" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="D132" s="5" t="n">
+        <v>942.879236</v>
+      </c>
+      <c r="E132" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F132" s="4" t="inlineStr">
+        <is>
+          <t>VES por USD</t>
+        </is>
+      </c>
+      <c r="G132" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H132" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I132" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J132" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K132" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01T21:01:21.677Z</t>
+        </is>
+      </c>
+      <c r="L132" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01T22:43:05Z</t>
+        </is>
+      </c>
+      <c r="M132" s="4" t="n"/>
+      <c r="N132" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_compra</t>
+        </is>
+      </c>
+      <c r="B133" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - compra</t>
+        </is>
+      </c>
+      <c r="C133" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="D133" s="5" t="n">
+        <v>957.9668</v>
+      </c>
+      <c r="E133" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F133" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G133" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H133" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I133" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J133" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K133" s="4" t="n"/>
+      <c r="L133" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01T22:43:05Z</t>
+        </is>
+      </c>
+      <c r="M133" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N133" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para compra. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_venta</t>
+        </is>
+      </c>
+      <c r="B134" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - venta</t>
+        </is>
+      </c>
+      <c r="C134" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="D134" s="5" t="n">
+        <v>958.1539</v>
+      </c>
+      <c r="E134" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F134" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G134" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H134" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I134" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J134" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K134" s="4" t="n"/>
+      <c r="L134" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01T22:43:05Z</t>
+        </is>
+      </c>
+      <c r="M134" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N134" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para venta. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N134"/>
+  <dimension ref="A1:N138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -8906,6 +8906,266 @@
         </is>
       </c>
     </row>
+    <row r="135">
+      <c r="A135" s="4" t="inlineStr">
+        <is>
+          <t>ve_eur_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B135" s="4" t="inlineStr">
+        <is>
+          <t>EUR paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C135" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="D135" s="5" t="n">
+        <v>1103.18395</v>
+      </c>
+      <c r="E135" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F135" s="4" t="inlineStr">
+        <is>
+          <t>VES por EUR</t>
+        </is>
+      </c>
+      <c r="G135" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H135" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I135" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J135" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K135" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02T21:01:11.665Z</t>
+        </is>
+      </c>
+      <c r="L135" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02T22:45:25Z</t>
+        </is>
+      </c>
+      <c r="M135" s="4" t="n"/>
+      <c r="N135" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="4" t="inlineStr">
+        <is>
+          <t>ve_usd_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B136" s="4" t="inlineStr">
+        <is>
+          <t>USD paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C136" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="D136" s="5" t="n">
+        <v>952.407387</v>
+      </c>
+      <c r="E136" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F136" s="4" t="inlineStr">
+        <is>
+          <t>VES por USD</t>
+        </is>
+      </c>
+      <c r="G136" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H136" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I136" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J136" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K136" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02T21:01:11.637Z</t>
+        </is>
+      </c>
+      <c r="L136" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02T22:45:25Z</t>
+        </is>
+      </c>
+      <c r="M136" s="4" t="n"/>
+      <c r="N136" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_compra</t>
+        </is>
+      </c>
+      <c r="B137" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - compra</t>
+        </is>
+      </c>
+      <c r="C137" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="D137" s="5" t="n">
+        <v>977.4719</v>
+      </c>
+      <c r="E137" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F137" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G137" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H137" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I137" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J137" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K137" s="4" t="n"/>
+      <c r="L137" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02T22:45:25Z</t>
+        </is>
+      </c>
+      <c r="M137" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N137" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para compra. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_venta</t>
+        </is>
+      </c>
+      <c r="B138" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - venta</t>
+        </is>
+      </c>
+      <c r="C138" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="D138" s="5" t="n">
+        <v>976.4416</v>
+      </c>
+      <c r="E138" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F138" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G138" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H138" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I138" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J138" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K138" s="4" t="n"/>
+      <c r="L138" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02T22:45:25Z</t>
+        </is>
+      </c>
+      <c r="M138" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N138" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para venta. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N138"/>
+  <dimension ref="A1:N142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -9166,6 +9166,266 @@
         </is>
       </c>
     </row>
+    <row r="139">
+      <c r="A139" s="4" t="inlineStr">
+        <is>
+          <t>ve_eur_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B139" s="4" t="inlineStr">
+        <is>
+          <t>EUR paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C139" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="D139" s="5" t="n">
+        <v>1101.823005</v>
+      </c>
+      <c r="E139" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F139" s="4" t="inlineStr">
+        <is>
+          <t>VES por EUR</t>
+        </is>
+      </c>
+      <c r="G139" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H139" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I139" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J139" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K139" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03T21:01:32.926Z</t>
+        </is>
+      </c>
+      <c r="L139" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03T22:43:33Z</t>
+        </is>
+      </c>
+      <c r="M139" s="4" t="n"/>
+      <c r="N139" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="4" t="inlineStr">
+        <is>
+          <t>ve_usd_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B140" s="4" t="inlineStr">
+        <is>
+          <t>USD paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C140" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="D140" s="5" t="n">
+        <v>948.041568</v>
+      </c>
+      <c r="E140" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F140" s="4" t="inlineStr">
+        <is>
+          <t>VES por USD</t>
+        </is>
+      </c>
+      <c r="G140" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H140" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I140" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J140" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K140" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03T21:01:32.852Z</t>
+        </is>
+      </c>
+      <c r="L140" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03T22:43:33Z</t>
+        </is>
+      </c>
+      <c r="M140" s="4" t="n"/>
+      <c r="N140" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_compra</t>
+        </is>
+      </c>
+      <c r="B141" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - compra</t>
+        </is>
+      </c>
+      <c r="C141" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="D141" s="5" t="n">
+        <v>973.412</v>
+      </c>
+      <c r="E141" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F141" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G141" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H141" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I141" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J141" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K141" s="4" t="n"/>
+      <c r="L141" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03T22:43:33Z</t>
+        </is>
+      </c>
+      <c r="M141" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N141" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para compra. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_venta</t>
+        </is>
+      </c>
+      <c r="B142" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - venta</t>
+        </is>
+      </c>
+      <c r="C142" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="D142" s="5" t="n">
+        <v>972.3967</v>
+      </c>
+      <c r="E142" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F142" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G142" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H142" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I142" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J142" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K142" s="4" t="n"/>
+      <c r="L142" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03T22:43:33Z</t>
+        </is>
+      </c>
+      <c r="M142" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N142" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para venta. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N142"/>
+  <dimension ref="A1:N146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -9426,6 +9426,266 @@
         </is>
       </c>
     </row>
+    <row r="143">
+      <c r="A143" s="4" t="inlineStr">
+        <is>
+          <t>ve_eur_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B143" s="4" t="inlineStr">
+        <is>
+          <t>EUR paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C143" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="D143" s="5" t="n">
+        <v>1093.932889</v>
+      </c>
+      <c r="E143" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F143" s="4" t="inlineStr">
+        <is>
+          <t>VES por EUR</t>
+        </is>
+      </c>
+      <c r="G143" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H143" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I143" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J143" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K143" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-04T21:01:19.276Z</t>
+        </is>
+      </c>
+      <c r="L143" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-04T22:26:35Z</t>
+        </is>
+      </c>
+      <c r="M143" s="4" t="n"/>
+      <c r="N143" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="4" t="inlineStr">
+        <is>
+          <t>ve_usd_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B144" s="4" t="inlineStr">
+        <is>
+          <t>USD paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C144" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="D144" s="5" t="n">
+        <v>942.833409</v>
+      </c>
+      <c r="E144" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F144" s="4" t="inlineStr">
+        <is>
+          <t>VES por USD</t>
+        </is>
+      </c>
+      <c r="G144" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H144" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I144" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J144" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K144" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-04T21:01:19.198Z</t>
+        </is>
+      </c>
+      <c r="L144" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-04T22:26:35Z</t>
+        </is>
+      </c>
+      <c r="M144" s="4" t="n"/>
+      <c r="N144" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_compra</t>
+        </is>
+      </c>
+      <c r="B145" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - compra</t>
+        </is>
+      </c>
+      <c r="C145" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="D145" s="5" t="n">
+        <v>963.934</v>
+      </c>
+      <c r="E145" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F145" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G145" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H145" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I145" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J145" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K145" s="4" t="n"/>
+      <c r="L145" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-04T22:26:35Z</t>
+        </is>
+      </c>
+      <c r="M145" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N145" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para compra. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_venta</t>
+        </is>
+      </c>
+      <c r="B146" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - venta</t>
+        </is>
+      </c>
+      <c r="C146" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="D146" s="5" t="n">
+        <v>961.53</v>
+      </c>
+      <c r="E146" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F146" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G146" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H146" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I146" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J146" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K146" s="4" t="n"/>
+      <c r="L146" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-04T22:26:35Z</t>
+        </is>
+      </c>
+      <c r="M146" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N146" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para venta. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N146"/>
+  <dimension ref="A1:N150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -9686,6 +9686,266 @@
         </is>
       </c>
     </row>
+    <row r="147">
+      <c r="A147" s="4" t="inlineStr">
+        <is>
+          <t>ve_eur_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B147" s="4" t="inlineStr">
+        <is>
+          <t>EUR paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C147" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="D147" s="5" t="n">
+        <v>1090.209903</v>
+      </c>
+      <c r="E147" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F147" s="4" t="inlineStr">
+        <is>
+          <t>VES por EUR</t>
+        </is>
+      </c>
+      <c r="G147" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H147" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I147" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J147" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K147" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-05T21:01:09.533Z</t>
+        </is>
+      </c>
+      <c r="L147" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-05T22:09:03Z</t>
+        </is>
+      </c>
+      <c r="M147" s="4" t="n"/>
+      <c r="N147" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="4" t="inlineStr">
+        <is>
+          <t>ve_usd_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B148" s="4" t="inlineStr">
+        <is>
+          <t>USD paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C148" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="D148" s="5" t="n">
+        <v>940.156683</v>
+      </c>
+      <c r="E148" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F148" s="4" t="inlineStr">
+        <is>
+          <t>VES por USD</t>
+        </is>
+      </c>
+      <c r="G148" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H148" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I148" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J148" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K148" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-05T21:01:09.459Z</t>
+        </is>
+      </c>
+      <c r="L148" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-05T22:09:03Z</t>
+        </is>
+      </c>
+      <c r="M148" s="4" t="n"/>
+      <c r="N148" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_compra</t>
+        </is>
+      </c>
+      <c r="B149" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - compra</t>
+        </is>
+      </c>
+      <c r="C149" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="D149" s="5" t="n">
+        <v>960.8765</v>
+      </c>
+      <c r="E149" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F149" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G149" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H149" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I149" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J149" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K149" s="4" t="n"/>
+      <c r="L149" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-05T22:09:03Z</t>
+        </is>
+      </c>
+      <c r="M149" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N149" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para compra. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_venta</t>
+        </is>
+      </c>
+      <c r="B150" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - venta</t>
+        </is>
+      </c>
+      <c r="C150" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="D150" s="5" t="n">
+        <v>956.9691</v>
+      </c>
+      <c r="E150" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F150" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G150" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H150" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I150" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J150" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K150" s="4" t="n"/>
+      <c r="L150" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-05T22:09:03Z</t>
+        </is>
+      </c>
+      <c r="M150" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N150" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para venta. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N150"/>
+  <dimension ref="A1:N154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -9946,6 +9946,266 @@
         </is>
       </c>
     </row>
+    <row r="151">
+      <c r="A151" s="4" t="inlineStr">
+        <is>
+          <t>ve_eur_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B151" s="4" t="inlineStr">
+        <is>
+          <t>EUR paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C151" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="D151" s="5" t="n">
+        <v>1098.01801</v>
+      </c>
+      <c r="E151" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F151" s="4" t="inlineStr">
+        <is>
+          <t>VES por EUR</t>
+        </is>
+      </c>
+      <c r="G151" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H151" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I151" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J151" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K151" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-06T21:00:59.065Z</t>
+        </is>
+      </c>
+      <c r="L151" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-06T22:12:17Z</t>
+        </is>
+      </c>
+      <c r="M151" s="4" t="n"/>
+      <c r="N151" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="4" t="inlineStr">
+        <is>
+          <t>ve_usd_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B152" s="4" t="inlineStr">
+        <is>
+          <t>USD paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C152" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="D152" s="5" t="n">
+        <v>946.258745</v>
+      </c>
+      <c r="E152" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F152" s="4" t="inlineStr">
+        <is>
+          <t>VES por USD</t>
+        </is>
+      </c>
+      <c r="G152" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H152" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I152" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J152" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K152" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-06T21:00:59.051Z</t>
+        </is>
+      </c>
+      <c r="L152" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-06T22:12:17Z</t>
+        </is>
+      </c>
+      <c r="M152" s="4" t="n"/>
+      <c r="N152" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_compra</t>
+        </is>
+      </c>
+      <c r="B153" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - compra</t>
+        </is>
+      </c>
+      <c r="C153" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="D153" s="5" t="n">
+        <v>958.2621</v>
+      </c>
+      <c r="E153" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F153" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G153" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H153" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I153" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J153" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K153" s="4" t="n"/>
+      <c r="L153" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-06T22:12:17Z</t>
+        </is>
+      </c>
+      <c r="M153" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N153" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para compra. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_venta</t>
+        </is>
+      </c>
+      <c r="B154" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - venta</t>
+        </is>
+      </c>
+      <c r="C154" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="D154" s="5" t="n">
+        <v>958.5999</v>
+      </c>
+      <c r="E154" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F154" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G154" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H154" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I154" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J154" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K154" s="4" t="n"/>
+      <c r="L154" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-06T22:12:17Z</t>
+        </is>
+      </c>
+      <c r="M154" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N154" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para venta. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N154"/>
+  <dimension ref="A1:N158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -10206,6 +10206,266 @@
         </is>
       </c>
     </row>
+    <row r="155">
+      <c r="A155" s="4" t="inlineStr">
+        <is>
+          <t>ve_eur_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B155" s="4" t="inlineStr">
+        <is>
+          <t>EUR paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C155" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="D155" s="5" t="n">
+        <v>1104.512544</v>
+      </c>
+      <c r="E155" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F155" s="4" t="inlineStr">
+        <is>
+          <t>VES por EUR</t>
+        </is>
+      </c>
+      <c r="G155" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H155" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I155" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J155" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K155" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-07T21:01:05.899Z</t>
+        </is>
+      </c>
+      <c r="L155" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-07T22:56:31Z</t>
+        </is>
+      </c>
+      <c r="M155" s="4" t="n"/>
+      <c r="N155" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="4" t="inlineStr">
+        <is>
+          <t>ve_usd_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B156" s="4" t="inlineStr">
+        <is>
+          <t>USD paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C156" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="D156" s="5" t="n">
+        <v>951.115633</v>
+      </c>
+      <c r="E156" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F156" s="4" t="inlineStr">
+        <is>
+          <t>VES por USD</t>
+        </is>
+      </c>
+      <c r="G156" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H156" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I156" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J156" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K156" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-07T21:01:05.839Z</t>
+        </is>
+      </c>
+      <c r="L156" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-07T22:56:31Z</t>
+        </is>
+      </c>
+      <c r="M156" s="4" t="n"/>
+      <c r="N156" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_compra</t>
+        </is>
+      </c>
+      <c r="B157" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - compra</t>
+        </is>
+      </c>
+      <c r="C157" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="D157" s="5" t="n">
+        <v>967.8244</v>
+      </c>
+      <c r="E157" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F157" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G157" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H157" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I157" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J157" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K157" s="4" t="n"/>
+      <c r="L157" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-07T22:56:31Z</t>
+        </is>
+      </c>
+      <c r="M157" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N157" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para compra. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_venta</t>
+        </is>
+      </c>
+      <c r="B158" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - venta</t>
+        </is>
+      </c>
+      <c r="C158" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="D158" s="5" t="n">
+        <v>969.0179000000001</v>
+      </c>
+      <c r="E158" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F158" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G158" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H158" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I158" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J158" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K158" s="4" t="n"/>
+      <c r="L158" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-07T22:56:31Z</t>
+        </is>
+      </c>
+      <c r="M158" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N158" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para venta. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N158"/>
+  <dimension ref="A1:N162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -10466,6 +10466,266 @@
         </is>
       </c>
     </row>
+    <row r="159">
+      <c r="A159" s="4" t="inlineStr">
+        <is>
+          <t>ve_eur_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B159" s="4" t="inlineStr">
+        <is>
+          <t>EUR paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C159" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="D159" s="5" t="n">
+        <v>1105.550361</v>
+      </c>
+      <c r="E159" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F159" s="4" t="inlineStr">
+        <is>
+          <t>VES por EUR</t>
+        </is>
+      </c>
+      <c r="G159" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H159" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I159" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J159" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K159" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-08T21:01:03.007Z</t>
+        </is>
+      </c>
+      <c r="L159" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-08T22:51:11Z</t>
+        </is>
+      </c>
+      <c r="M159" s="4" t="n"/>
+      <c r="N159" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="4" t="inlineStr">
+        <is>
+          <t>ve_usd_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B160" s="4" t="inlineStr">
+        <is>
+          <t>USD paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C160" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="D160" s="5" t="n">
+        <v>951.801472</v>
+      </c>
+      <c r="E160" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F160" s="4" t="inlineStr">
+        <is>
+          <t>VES por USD</t>
+        </is>
+      </c>
+      <c r="G160" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H160" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I160" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J160" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K160" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-08T21:01:02.992Z</t>
+        </is>
+      </c>
+      <c r="L160" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-08T22:51:11Z</t>
+        </is>
+      </c>
+      <c r="M160" s="4" t="n"/>
+      <c r="N160" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_compra</t>
+        </is>
+      </c>
+      <c r="B161" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - compra</t>
+        </is>
+      </c>
+      <c r="C161" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="D161" s="5" t="n">
+        <v>967.3474</v>
+      </c>
+      <c r="E161" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F161" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G161" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H161" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I161" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J161" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K161" s="4" t="n"/>
+      <c r="L161" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-08T22:51:11Z</t>
+        </is>
+      </c>
+      <c r="M161" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N161" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para compra. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_venta</t>
+        </is>
+      </c>
+      <c r="B162" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - venta</t>
+        </is>
+      </c>
+      <c r="C162" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="D162" s="5" t="n">
+        <v>966.8981</v>
+      </c>
+      <c r="E162" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F162" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G162" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H162" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I162" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J162" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K162" s="4" t="n"/>
+      <c r="L162" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-08T22:51:11Z</t>
+        </is>
+      </c>
+      <c r="M162" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N162" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para venta. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N162"/>
+  <dimension ref="A1:N166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -10726,6 +10726,266 @@
         </is>
       </c>
     </row>
+    <row r="163">
+      <c r="A163" s="4" t="inlineStr">
+        <is>
+          <t>ve_eur_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B163" s="4" t="inlineStr">
+        <is>
+          <t>EUR paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C163" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="D163" s="5" t="n">
+        <v>1098.662407</v>
+      </c>
+      <c r="E163" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F163" s="4" t="inlineStr">
+        <is>
+          <t>VES por EUR</t>
+        </is>
+      </c>
+      <c r="G163" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H163" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I163" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J163" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K163" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09T21:01:16.663Z</t>
+        </is>
+      </c>
+      <c r="L163" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09T22:40:16Z</t>
+        </is>
+      </c>
+      <c r="M163" s="4" t="n"/>
+      <c r="N163" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="4" t="inlineStr">
+        <is>
+          <t>ve_usd_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B164" s="4" t="inlineStr">
+        <is>
+          <t>USD paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C164" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="D164" s="5" t="n">
+        <v>945.976898</v>
+      </c>
+      <c r="E164" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F164" s="4" t="inlineStr">
+        <is>
+          <t>VES por USD</t>
+        </is>
+      </c>
+      <c r="G164" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H164" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I164" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J164" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K164" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09T21:01:16.601Z</t>
+        </is>
+      </c>
+      <c r="L164" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09T22:40:16Z</t>
+        </is>
+      </c>
+      <c r="M164" s="4" t="n"/>
+      <c r="N164" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_compra</t>
+        </is>
+      </c>
+      <c r="B165" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - compra</t>
+        </is>
+      </c>
+      <c r="C165" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="D165" s="5" t="n">
+        <v>965.8630000000001</v>
+      </c>
+      <c r="E165" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F165" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G165" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H165" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I165" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J165" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K165" s="4" t="n"/>
+      <c r="L165" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09T22:40:16Z</t>
+        </is>
+      </c>
+      <c r="M165" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N165" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para compra. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_venta</t>
+        </is>
+      </c>
+      <c r="B166" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - venta</t>
+        </is>
+      </c>
+      <c r="C166" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="D166" s="5" t="n">
+        <v>964.8867</v>
+      </c>
+      <c r="E166" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F166" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G166" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H166" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I166" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J166" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K166" s="4" t="n"/>
+      <c r="L166" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09T22:40:16Z</t>
+        </is>
+      </c>
+      <c r="M166" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N166" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para venta. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N166"/>
+  <dimension ref="A1:N170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -10986,6 +10986,266 @@
         </is>
       </c>
     </row>
+    <row r="167">
+      <c r="A167" s="4" t="inlineStr">
+        <is>
+          <t>ve_eur_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B167" s="4" t="inlineStr">
+        <is>
+          <t>EUR paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C167" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="D167" s="5" t="n">
+        <v>1092.582175</v>
+      </c>
+      <c r="E167" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F167" s="4" t="inlineStr">
+        <is>
+          <t>VES por EUR</t>
+        </is>
+      </c>
+      <c r="G167" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H167" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I167" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J167" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K167" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-10T21:01:09.667Z</t>
+        </is>
+      </c>
+      <c r="L167" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-10T22:42:16Z</t>
+        </is>
+      </c>
+      <c r="M167" s="4" t="n"/>
+      <c r="N167" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="4" t="inlineStr">
+        <is>
+          <t>ve_usd_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B168" s="4" t="inlineStr">
+        <is>
+          <t>USD paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C168" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="D168" s="5" t="n">
+        <v>941.783983</v>
+      </c>
+      <c r="E168" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F168" s="4" t="inlineStr">
+        <is>
+          <t>VES por USD</t>
+        </is>
+      </c>
+      <c r="G168" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H168" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I168" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J168" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K168" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-10T21:01:09.608Z</t>
+        </is>
+      </c>
+      <c r="L168" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-10T22:42:16Z</t>
+        </is>
+      </c>
+      <c r="M168" s="4" t="n"/>
+      <c r="N168" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_compra</t>
+        </is>
+      </c>
+      <c r="B169" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - compra</t>
+        </is>
+      </c>
+      <c r="C169" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="D169" s="5" t="n">
+        <v>961.0880999999999</v>
+      </c>
+      <c r="E169" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F169" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G169" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H169" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I169" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J169" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K169" s="4" t="n"/>
+      <c r="L169" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-10T22:42:16Z</t>
+        </is>
+      </c>
+      <c r="M169" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N169" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para compra. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_venta</t>
+        </is>
+      </c>
+      <c r="B170" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - venta</t>
+        </is>
+      </c>
+      <c r="C170" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="D170" s="5" t="n">
+        <v>962.4179</v>
+      </c>
+      <c r="E170" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F170" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G170" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H170" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I170" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J170" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K170" s="4" t="n"/>
+      <c r="L170" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-10T22:42:16Z</t>
+        </is>
+      </c>
+      <c r="M170" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N170" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para venta. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N170"/>
+  <dimension ref="A1:N174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -11246,6 +11246,266 @@
         </is>
       </c>
     </row>
+    <row r="171">
+      <c r="A171" s="4" t="inlineStr">
+        <is>
+          <t>ve_eur_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B171" s="4" t="inlineStr">
+        <is>
+          <t>EUR paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C171" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="D171" s="5" t="n">
+        <v>1097.166668</v>
+      </c>
+      <c r="E171" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F171" s="4" t="inlineStr">
+        <is>
+          <t>VES por EUR</t>
+        </is>
+      </c>
+      <c r="G171" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H171" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I171" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J171" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K171" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-11T21:01:16.909Z</t>
+        </is>
+      </c>
+      <c r="L171" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-11T22:42:29Z</t>
+        </is>
+      </c>
+      <c r="M171" s="4" t="n"/>
+      <c r="N171" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="4" t="inlineStr">
+        <is>
+          <t>ve_usd_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B172" s="4" t="inlineStr">
+        <is>
+          <t>USD paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C172" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="D172" s="5" t="n">
+        <v>947.304673</v>
+      </c>
+      <c r="E172" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F172" s="4" t="inlineStr">
+        <is>
+          <t>VES por USD</t>
+        </is>
+      </c>
+      <c r="G172" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H172" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I172" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J172" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K172" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-11T21:01:16.848Z</t>
+        </is>
+      </c>
+      <c r="L172" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-11T22:42:29Z</t>
+        </is>
+      </c>
+      <c r="M172" s="4" t="n"/>
+      <c r="N172" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_compra</t>
+        </is>
+      </c>
+      <c r="B173" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - compra</t>
+        </is>
+      </c>
+      <c r="C173" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="D173" s="5" t="n">
+        <v>961.0060999999999</v>
+      </c>
+      <c r="E173" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F173" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G173" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H173" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I173" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J173" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K173" s="4" t="n"/>
+      <c r="L173" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-11T22:42:29Z</t>
+        </is>
+      </c>
+      <c r="M173" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N173" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para compra. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_venta</t>
+        </is>
+      </c>
+      <c r="B174" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - venta</t>
+        </is>
+      </c>
+      <c r="C174" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="D174" s="5" t="n">
+        <v>960.6596</v>
+      </c>
+      <c r="E174" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F174" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G174" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H174" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I174" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J174" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K174" s="4" t="n"/>
+      <c r="L174" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-11T22:42:29Z</t>
+        </is>
+      </c>
+      <c r="M174" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N174" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para venta. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
+++ b/assets/data/tipo-cambio/excel/ve_tipo_cambio_referencias_mercado.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N174"/>
+  <dimension ref="A1:N178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -11506,6 +11506,266 @@
         </is>
       </c>
     </row>
+    <row r="175">
+      <c r="A175" s="4" t="inlineStr">
+        <is>
+          <t>ve_eur_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B175" s="4" t="inlineStr">
+        <is>
+          <t>EUR paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C175" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="D175" s="5" t="n">
+        <v>1094.697778</v>
+      </c>
+      <c r="E175" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F175" s="4" t="inlineStr">
+        <is>
+          <t>VES por EUR</t>
+        </is>
+      </c>
+      <c r="G175" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H175" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I175" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J175" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K175" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-12T21:01:19.874Z</t>
+        </is>
+      </c>
+      <c r="L175" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-12T22:26:48Z</t>
+        </is>
+      </c>
+      <c r="M175" s="4" t="n"/>
+      <c r="N175" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="4" t="inlineStr">
+        <is>
+          <t>ve_usd_paralelo_dolarapi</t>
+        </is>
+      </c>
+      <c r="B176" s="4" t="inlineStr">
+        <is>
+          <t>USD paralelo - DolarApi</t>
+        </is>
+      </c>
+      <c r="C176" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="D176" s="5" t="n">
+        <v>945.165346</v>
+      </c>
+      <c r="E176" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F176" s="4" t="inlineStr">
+        <is>
+          <t>VES por USD</t>
+        </is>
+      </c>
+      <c r="G176" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H176" s="4" t="inlineStr">
+        <is>
+          <t>DolarApi Venezuela</t>
+        </is>
+      </c>
+      <c r="I176" s="4" t="inlineStr">
+        <is>
+          <t>https://dolarapi.com/docs/venezuela/</t>
+        </is>
+      </c>
+      <c r="J176" s="4" t="inlineStr">
+        <is>
+          <t>market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K176" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-12T21:01:19.824Z</t>
+        </is>
+      </c>
+      <c r="L176" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-12T22:26:48Z</t>
+        </is>
+      </c>
+      <c r="M176" s="4" t="n"/>
+      <c r="N176" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mercado no oficial provista por DolarApi a partir de fuentes públicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_compra</t>
+        </is>
+      </c>
+      <c r="B177" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - compra</t>
+        </is>
+      </c>
+      <c r="C177" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="D177" s="5" t="n">
+        <v>956.0436</v>
+      </c>
+      <c r="E177" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F177" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G177" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H177" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I177" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J177" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K177" s="4" t="n"/>
+      <c r="L177" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-12T22:26:48Z</t>
+        </is>
+      </c>
+      <c r="M177" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N177" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para compra. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="4" t="inlineStr">
+        <is>
+          <t>ve_usdt_binance_p2p_venta</t>
+        </is>
+      </c>
+      <c r="B178" s="4" t="inlineStr">
+        <is>
+          <t>USDT/VES Binance P2P - venta</t>
+        </is>
+      </c>
+      <c r="C178" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="D178" s="5" t="n">
+        <v>957.147</v>
+      </c>
+      <c r="E178" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="F178" s="4" t="inlineStr">
+        <is>
+          <t>VES por USDT</t>
+        </is>
+      </c>
+      <c r="G178" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="H178" s="4" t="inlineStr">
+        <is>
+          <t>Binance P2P</t>
+        </is>
+      </c>
+      <c r="I178" s="4" t="inlineStr">
+        <is>
+          <t>https://www.binance.com/en/price/tether/VES</t>
+        </is>
+      </c>
+      <c r="J178" s="4" t="inlineStr">
+        <is>
+          <t>digital_market_reference_non_official</t>
+        </is>
+      </c>
+      <c r="K178" s="4" t="n"/>
+      <c r="L178" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-12T22:26:48Z</t>
+        </is>
+      </c>
+      <c r="M178" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N178" s="4" t="inlineStr">
+        <is>
+          <t>Promedio simple OVE de las primeras 10 ofertas visibles en Binance P2P para venta. No es tasa oficial.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
